--- a/Frahm_etal_1984/Frahm_etal_1984_Table1_snapshot.xlsx
+++ b/Frahm_etal_1984/Frahm_etal_1984_Table1_snapshot.xlsx
@@ -1,34 +1,199 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/Frahm_etal_1984/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_097F074C6299B51CD65C4A0A68361804CD8DCAB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6E365FF-8AE5-5445-A8E7-055B2894E55C}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="4220" yWindow="900" windowWidth="10000" windowHeight="20520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Table1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+  <si>
+    <t>Table 1. Frahm, Stephan &amp; Baron (1984) area striata (V1) volumes. Volumes in mm³ (body weight g, brain weight mg). [Snapshot: values taken from the curated comparison CSV Frahm_1984.csv.]</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>Area_striata_mm3</t>
+  </si>
+  <si>
+    <t>Area_striata_grey_matter_mm3</t>
+  </si>
+  <si>
+    <t>Area_striata_lamina_1_mm3</t>
+  </si>
+  <si>
+    <t>Area_striata_laminae_2_6_mm3</t>
+  </si>
+  <si>
+    <t>Area_striata_white_matter_mm3</t>
+  </si>
+  <si>
+    <t>Alouatta sp.</t>
+  </si>
+  <si>
+    <t>Aotus trivirgatus</t>
+  </si>
+  <si>
+    <t>Ateles geoffroyi</t>
+  </si>
+  <si>
+    <t>Avahi l. laniger</t>
+  </si>
+  <si>
+    <t>Avahi laniger occidentalis</t>
+  </si>
+  <si>
+    <t>Callicebus moloch</t>
+  </si>
+  <si>
+    <t>Callithrix jacchus</t>
+  </si>
+  <si>
+    <t>Cebuella pygmaea</t>
+  </si>
+  <si>
+    <t>Cebus sp.</t>
+  </si>
+  <si>
+    <t>Cercopithecus ascanius</t>
+  </si>
+  <si>
+    <t>Cercopithecus mitis</t>
+  </si>
+  <si>
+    <t>Cheirogaleus major</t>
+  </si>
+  <si>
+    <t>Cheirogaleus medius</t>
+  </si>
+  <si>
+    <t>Daubentonia madagascar.</t>
+  </si>
+  <si>
+    <t>Lemur albifrons</t>
+  </si>
+  <si>
+    <t>Galago senegalensis</t>
+  </si>
+  <si>
+    <t>Galagoides demidoff</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Hylobates lar</t>
+  </si>
+  <si>
+    <t>Indri indri</t>
+  </si>
+  <si>
+    <t>Lagothrix lagothricha</t>
+  </si>
+  <si>
+    <t>Lepilemur ruficaudatus</t>
+  </si>
+  <si>
+    <t>Cercocebus albigena</t>
+  </si>
+  <si>
+    <t>Loris tardigradus</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Miopithecus talapoin</t>
+  </si>
+  <si>
+    <t>Nycticebus coucang</t>
+  </si>
+  <si>
+    <t>Otolemur crassicaudatus</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Perodicticus potto</t>
+  </si>
+  <si>
+    <t>Colobus badius</t>
+  </si>
+  <si>
+    <t>Pithecia monachus</t>
+  </si>
+  <si>
+    <t>Propithecus verreauxi</t>
+  </si>
+  <si>
+    <t>Saguinus midas</t>
+  </si>
+  <si>
+    <t>Saguinus oedipus</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Tarsius sp.</t>
+  </si>
+  <si>
+    <t>Tupaia glis</t>
+  </si>
+  <si>
+    <t>Tupaia minor</t>
+  </si>
+  <si>
+    <t>Urogale everetti</t>
+  </si>
+  <si>
+    <t>Varecia variegata</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +212,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,1041 +514,936 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="24.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Table 1. Frahm, Stephan &amp; Baron (1984) area striata (V1) volumes. Volumes in mm³ (body weight g, brain weight mg). [Snapshot: values taken from the curated comparison CSV Frahm_1984.csv.]</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Species</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Area_striata_mm3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Area_striata_grey_matter_mm3</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Area_striata_lamina_1_mm3</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Area_striata_laminae_2_6_mm3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Area_striata_white_matter_mm3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Alouatta sp.</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
         <v>2461</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>1918</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>220</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>1698</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>543</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Aotus trivirgatus</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>1203</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>996</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>113</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>883</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>207</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <v>4738</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>3753</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>985</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Avahi l. laniger</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
         <v>542</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>475</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>66.5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Avahi laniger occidentalis</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>527</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>450</v>
       </c>
-      <c r="E7" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="F7">
         <v>385</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>77.2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Callicebus moloch</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>1524</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>1201</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>324</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>685</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>566</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>57.8</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>508</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>119</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cebuella pygmaea</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>415</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>363</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>29.7</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>334</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>51.4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cebus sp.</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>4703</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>3764</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>365</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>3399</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>939</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cercopithecus ascanius</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
         <v>5106</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>4272</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>416</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>3855</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>834</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cercopithecus mitis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
         <v>5275</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>4232</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>1042</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cheirogaleus major</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
         <v>2</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>477</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>433</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>44.8</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cheirogaleus medius</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>216</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>199</v>
       </c>
-      <c r="G15" t="n">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Daubentonia madagascar.</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="G15">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
         <v>1355</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>1113</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>189</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>923</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>242</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lemur albifrons</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1519</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>1253</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>138</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1114</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>267</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="n">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
         <v>334</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>301</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>32.6</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Galagoides demidoff</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>237</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>214</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>25.6</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>189</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>22.4</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="n">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
         <v>15185</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>12062</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3123</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="n">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
         <v>20226</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>14787</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>1704</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>13083</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>5439</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Hylobates lar</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="n">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
         <v>5750</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>4574</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>562</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>4012</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>1176</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Indri indri</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>1961</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>1648</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>279</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>1369</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>313</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Lagothrix lagothricha</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="n">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
         <v>6082</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>4856</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>604</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>4252</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>1226</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Lepilemur ruficaudatus</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>358</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>326</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>52.5</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>274</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>31.4</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cercocebus albigena</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="n">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
         <v>6831</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>5420</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>1411</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Loris tardigradus</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="n">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
         <v>588</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>529</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>59.6</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="n">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
         <v>6586</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>5343</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>1243</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29">
         <v>5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>144</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>136</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>15</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>121</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>8.24</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Miopithecus talapoin</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
         <v>3048</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>2339</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>709</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Nycticebus coucang</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
         <v>828</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>696</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>93.8</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>603</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>132</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Otolemur crassicaudatus</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
         <v>548</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>479</v>
       </c>
-      <c r="G32" t="n">
-        <v>68.40000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="n">
+      <c r="G32">
+        <v>68.400000000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
         <v>14597</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>10593</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>1156</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>9437</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>4004</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
         <v>13741</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>10001</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>919</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>9082</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>3740</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Perodicticus potto</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35">
         <v>2</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>552</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>495</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>57.7</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Colobus badius</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36">
         <v>2</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>3979</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>3053</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>360</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>2693</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>926</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Pithecia monachus</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
         <v>2130</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>1679</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>451</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Propithecus verreauxi</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38">
         <v>2</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>1355</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>1106</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>131</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>974</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>249</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Saguinus midas</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="n">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
         <v>1061</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>841</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>220</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Saguinus oedipus</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
         <v>977</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>807</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>170</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="n">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
         <v>2326</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>1884</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>175</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>1709</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>442</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Tarsius sp.</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42">
         <v>2</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>370</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>349</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>41.2</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>307</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>21.3</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Tupaia glis</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43">
         <v>4</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>179</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>169</v>
       </c>
-      <c r="E43" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F43" t="n">
+      <c r="E43">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F43">
         <v>149</v>
       </c>
-      <c r="G43" t="n">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Tupaia minor</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
+      <c r="G43">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44">
         <v>2</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>164</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>152</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>12.5</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Urogale everetti</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="n">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
         <v>136</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>123</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>15.5</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>108</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>12.7</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Varecia variegata</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
         <v>2112</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>1745</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>367</v>
       </c>
     </row>
@@ -1452,6 +1453,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1706,34 +1727,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD8264A3-1CAD-4AA4-9208-9938EEFD1759}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D714CB8-C311-46F4-A900-CFFA679B2640}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AA7D4D-2E2B-4907-8719-FDAD1C6C4589}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AA7D4D-2E2B-4907-8719-FDAD1C6C4589}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D714CB8-C311-46F4-A900-CFFA679B2640}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD8264A3-1CAD-4AA4-9208-9938EEFD1759}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>